--- a/time-spent.xlsx
+++ b/time-spent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\smccann-software\smwebman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15AE898-9A6A-45AE-A79D-43D35D961330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A622B06-35C4-491A-96F5-7BF4D7C43D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A10B42A8-E862-4DE3-8908-170894873712}"/>
   </bookViews>
@@ -35,10 +35,41 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+  <si>
+    <t>Content and basic structure</t>
+  </si>
+  <si>
+    <t>Total Time</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -66,10 +97,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,28 +437,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDC7E68-DEF6-4655-B185-A65A633E6874}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="4">
+        <f>SUM(D:D)</f>
+        <v>3.6111111111111094E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>45862</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B2" s="2">
         <v>0.31388888888888888</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C2" s="2">
         <v>0.33611111111111114</v>
       </c>
-      <c r="D1" s="2">
-        <f>C1-B1</f>
+      <c r="D2" s="2">
+        <f>C2-B2</f>
         <v>2.2222222222222254E-2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>45862</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3-B3</f>
+        <v>1.388888888888884E-2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/time-spent.xlsx
+++ b/time-spent.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\smccann-software\smwebman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A622B06-35C4-491A-96F5-7BF4D7C43D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63102A29-E3E5-4EE7-9A98-0CA5D555E4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A10B42A8-E862-4DE3-8908-170894873712}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t>Content and basic structure</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Tasks</t>
+  </si>
+  <si>
+    <t>Logo</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDC7E68-DEF6-4655-B185-A65A633E6874}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -469,7 +472,7 @@
       </c>
       <c r="M1" s="4">
         <f>SUM(D:D)</f>
-        <v>3.6111111111111094E-2</v>
+        <v>0.27569444444444441</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -505,6 +508,84 @@
         <v>1.388888888888884E-2</v>
       </c>
       <c r="F3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>45878</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D10" si="0">C4-B4</f>
+        <v>0.10416666666666669</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.78125</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>7.291666666666663E-2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/time-spent.xlsx
+++ b/time-spent.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\smccann-software\smwebman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63102A29-E3E5-4EE7-9A98-0CA5D555E4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D904E-DF11-43D5-81D8-D229B646DF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A10B42A8-E862-4DE3-8908-170894873712}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{A10B42A8-E862-4DE3-8908-170894873712}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>Content and basic structure</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Logo</t>
+  </si>
+  <si>
+    <t>Styling</t>
   </si>
 </sst>
 </file>
@@ -472,7 +475,7 @@
       </c>
       <c r="M1" s="4">
         <f>SUM(D:D)</f>
-        <v>0.27569444444444441</v>
+        <v>0.35555555555555557</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -566,15 +569,39 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45880</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.84027777777777779</v>
+      </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.777777777777779E-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45880</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.9375</v>
+      </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.208333333333337E-2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">

--- a/time-spent.xlsx
+++ b/time-spent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\smccann-software\smwebman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D904E-DF11-43D5-81D8-D229B646DF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CC6755C-3BF4-49AB-9042-A843A38DC8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{A10B42A8-E862-4DE3-8908-170894873712}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Content and basic structure</t>
   </si>
@@ -60,6 +61,12 @@
   </si>
   <si>
     <t>Styling</t>
+  </si>
+  <si>
+    <t>Background image size</t>
+  </si>
+  <si>
+    <t>404 page, cookie page</t>
   </si>
 </sst>
 </file>
@@ -475,7 +482,7 @@
       </c>
       <c r="M1" s="4">
         <f>SUM(D:D)</f>
-        <v>0.35555555555555557</v>
+        <v>0.41458333333333341</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -605,15 +612,39 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45881</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.86458333333333337</v>
+      </c>
       <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.1666666666666741E-2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45883</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.30902777777777779</v>
+      </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7361111111111105E-2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
